--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/204.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/204.xlsx
@@ -426,13 +426,13 @@
         <v>-14.04687964555674</v>
       </c>
       <c r="E2">
-        <v>-21.00298301175058</v>
+        <v>-25.23625938428293</v>
       </c>
       <c r="F2">
-        <v>0.6869294202336578</v>
+        <v>-0.09157923144257314</v>
       </c>
       <c r="G2">
-        <v>-14.73920537952043</v>
+        <v>-20.27483809719211</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.98478381525859</v>
       </c>
       <c r="E3">
-        <v>-21.50558022796588</v>
+        <v>-26.92715987942899</v>
       </c>
       <c r="F3">
-        <v>0.9242699235450751</v>
+        <v>-0.8690046282726435</v>
       </c>
       <c r="G3">
-        <v>-15.7381525643589</v>
+        <v>-19.72798397701483</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.82709163797845</v>
       </c>
       <c r="E4">
-        <v>-21.67855887811088</v>
+        <v>-28.30685458381992</v>
       </c>
       <c r="F4">
-        <v>0.9146013989313173</v>
+        <v>-1.207201067249949</v>
       </c>
       <c r="G4">
-        <v>-15.13165896629165</v>
+        <v>-18.98041479133708</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.56230668481484</v>
       </c>
       <c r="E5">
-        <v>-21.51215557222502</v>
+        <v>-26.47366490687886</v>
       </c>
       <c r="F5">
-        <v>0.8801051166812153</v>
+        <v>-0.9411519349564029</v>
       </c>
       <c r="G5">
-        <v>-15.44075136111124</v>
+        <v>-20.09221681833652</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.18310678797447</v>
       </c>
       <c r="E6">
-        <v>-21.2070315220622</v>
+        <v>-29.30219958528385</v>
       </c>
       <c r="F6">
-        <v>1.246180322740959</v>
+        <v>-1.192352240586789</v>
       </c>
       <c r="G6">
-        <v>-14.153665879444</v>
+        <v>-20.37489933611658</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.68663284238438</v>
       </c>
       <c r="E7">
-        <v>-22.48268453612691</v>
+        <v>-27.40733662083231</v>
       </c>
       <c r="F7">
-        <v>1.418082097626418</v>
+        <v>-0.7695716523717778</v>
       </c>
       <c r="G7">
-        <v>-15.21119978869095</v>
+        <v>-18.88428648051326</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.06996994160821</v>
       </c>
       <c r="E8">
-        <v>-22.47668883654075</v>
+        <v>-29.14715369220923</v>
       </c>
       <c r="F8">
-        <v>1.098881419251851</v>
+        <v>0.287064264762098</v>
       </c>
       <c r="G8">
-        <v>-13.81980067235404</v>
+        <v>-16.71887850654921</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.33681801172054</v>
       </c>
       <c r="E9">
-        <v>-23.54881864327873</v>
+        <v>-31.70950013996935</v>
       </c>
       <c r="F9">
-        <v>1.119466428740733</v>
+        <v>-0.0716688806736684</v>
       </c>
       <c r="G9">
-        <v>-13.49716318046052</v>
+        <v>-17.29406096490603</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.50524696736312</v>
       </c>
       <c r="E10">
-        <v>-25.48300234753887</v>
+        <v>-29.21299317580675</v>
       </c>
       <c r="F10">
-        <v>1.093705868320195</v>
+        <v>-0.1288279945737089</v>
       </c>
       <c r="G10">
-        <v>-12.77435025432544</v>
+        <v>-17.35217759184794</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.595035879725778</v>
       </c>
       <c r="E11">
-        <v>-25.00252672685103</v>
+        <v>-33.21062587487597</v>
       </c>
       <c r="F11">
-        <v>1.581769189928493</v>
+        <v>-0.7479342703020864</v>
       </c>
       <c r="G11">
-        <v>-11.74522082580544</v>
+        <v>-17.77291979025222</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.631531077118606</v>
       </c>
       <c r="E12">
-        <v>-25.30818060847275</v>
+        <v>-31.17439753732699</v>
       </c>
       <c r="F12">
-        <v>1.344911716921285</v>
+        <v>-0.4431952024943547</v>
       </c>
       <c r="G12">
-        <v>-11.82808709119893</v>
+        <v>-16.28001272659019</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.641475124129421</v>
       </c>
       <c r="E13">
-        <v>-25.57524736307511</v>
+        <v>-31.62016466898303</v>
       </c>
       <c r="F13">
-        <v>1.321121286659554</v>
+        <v>-0.02849705741878907</v>
       </c>
       <c r="G13">
-        <v>-11.5359016524484</v>
+        <v>-17.86087601941235</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.670374143997972</v>
       </c>
       <c r="E14">
-        <v>-27.93556499993103</v>
+        <v>-29.14852581983355</v>
       </c>
       <c r="F14">
-        <v>1.391957284845329</v>
+        <v>-0.9568393339017884</v>
       </c>
       <c r="G14">
-        <v>-10.52319252980318</v>
+        <v>-15.9785081021466</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.757283666817224</v>
       </c>
       <c r="E15">
-        <v>-27.31732414298185</v>
+        <v>-33.74709154819463</v>
       </c>
       <c r="F15">
-        <v>1.763754420377556</v>
+        <v>-0.2128024170339702</v>
       </c>
       <c r="G15">
-        <v>-9.990860117633916</v>
+        <v>-13.7562564060005</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.937311642713491</v>
       </c>
       <c r="E16">
-        <v>-29.10992057891816</v>
+        <v>-34.27502557648285</v>
       </c>
       <c r="F16">
-        <v>1.959666760646992</v>
+        <v>-0.05293839081176606</v>
       </c>
       <c r="G16">
-        <v>-10.52907536922647</v>
+        <v>-13.96839285361146</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.235240266898705</v>
       </c>
       <c r="E17">
-        <v>-28.76111034000334</v>
+        <v>-34.60135647042359</v>
       </c>
       <c r="F17">
-        <v>1.571874195368828</v>
+        <v>0.3154569444140964</v>
       </c>
       <c r="G17">
-        <v>-10.35279544035136</v>
+        <v>-14.28161846453683</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.677019961384365</v>
       </c>
       <c r="E18">
-        <v>-30.47860203452245</v>
+        <v>-30.63152633752447</v>
       </c>
       <c r="F18">
-        <v>2.081873427611877</v>
+        <v>0.1287229717775889</v>
       </c>
       <c r="G18">
-        <v>-8.589539296315817</v>
+        <v>-13.23150017729785</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.275059228992552</v>
       </c>
       <c r="E19">
-        <v>-32.52714782137228</v>
+        <v>-34.64206971598955</v>
       </c>
       <c r="F19">
-        <v>2.228405817437912</v>
+        <v>0.5103921381337071</v>
       </c>
       <c r="G19">
-        <v>-8.438707531001082</v>
+        <v>-15.01456000474932</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.030877529613805</v>
       </c>
       <c r="E20">
-        <v>-31.09073850850929</v>
+        <v>-37.2155947018376</v>
       </c>
       <c r="F20">
-        <v>2.494603026234552</v>
+        <v>1.197303990778667</v>
       </c>
       <c r="G20">
-        <v>-8.617966950861538</v>
+        <v>-14.2957776678083</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.934600121293026</v>
       </c>
       <c r="E21">
-        <v>-32.13531255091059</v>
+        <v>-39.01548877363727</v>
       </c>
       <c r="F21">
-        <v>3.176502449657145</v>
+        <v>0.429344404205178</v>
       </c>
       <c r="G21">
-        <v>-8.570960514749427</v>
+        <v>-11.5603400996193</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.973841594520004</v>
       </c>
       <c r="E22">
-        <v>-31.94403660153761</v>
+        <v>-37.4385790262123</v>
       </c>
       <c r="F22">
-        <v>2.863834558183767</v>
+        <v>0.4878662970454541</v>
       </c>
       <c r="G22">
-        <v>-7.343248012056246</v>
+        <v>-12.92628774185029</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.130151450720847</v>
       </c>
       <c r="E23">
-        <v>-32.51305973873442</v>
+        <v>-36.0979876948776</v>
       </c>
       <c r="F23">
-        <v>3.259523481156312</v>
+        <v>1.592946986279665</v>
       </c>
       <c r="G23">
-        <v>-8.577863002198807</v>
+        <v>-13.74636946174747</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.381292555420329</v>
       </c>
       <c r="E24">
-        <v>-33.02513505104778</v>
+        <v>-37.56817715960081</v>
       </c>
       <c r="F24">
-        <v>3.330174185749982</v>
+        <v>1.382439212293538</v>
       </c>
       <c r="G24">
-        <v>-9.10222031016397</v>
+        <v>-13.58525183144222</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.701579330980538</v>
       </c>
       <c r="E25">
-        <v>-33.17924355000281</v>
+        <v>-38.40179224035479</v>
       </c>
       <c r="F25">
-        <v>3.368867288675998</v>
+        <v>1.389084442314722</v>
       </c>
       <c r="G25">
-        <v>-6.442779625374484</v>
+        <v>-13.55067814910284</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.066569928071139</v>
       </c>
       <c r="E26">
-        <v>-33.96171404531416</v>
+        <v>-39.75888985944745</v>
       </c>
       <c r="F26">
-        <v>3.000530550569007</v>
+        <v>0.9982099853251121</v>
       </c>
       <c r="G26">
-        <v>-8.286935570753194</v>
+        <v>-12.65389274433351</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.453536702215501</v>
       </c>
       <c r="E27">
-        <v>-33.74053431783152</v>
+        <v>-39.5399992755757</v>
       </c>
       <c r="F27">
-        <v>3.02585875927463</v>
+        <v>1.594231371777086</v>
       </c>
       <c r="G27">
-        <v>-8.089276138785468</v>
+        <v>-13.25454819534226</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.844831552499794</v>
       </c>
       <c r="E28">
-        <v>-34.22914081360013</v>
+        <v>-37.88966032211634</v>
       </c>
       <c r="F28">
-        <v>3.247979848738674</v>
+        <v>0.9749390106036449</v>
       </c>
       <c r="G28">
-        <v>-7.969245689168114</v>
+        <v>-14.39105516842852</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.223475750217943</v>
       </c>
       <c r="E29">
-        <v>-34.51077793332217</v>
+        <v>-37.92898785463596</v>
       </c>
       <c r="F29">
-        <v>3.125481779885348</v>
+        <v>0.5800451080006495</v>
       </c>
       <c r="G29">
-        <v>-7.246775404496344</v>
+        <v>-13.04163376952957</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.575151779163913</v>
       </c>
       <c r="E30">
-        <v>-32.10525933315868</v>
+        <v>-37.68332040395684</v>
       </c>
       <c r="F30">
-        <v>3.128105980587232</v>
+        <v>1.030766227828801</v>
       </c>
       <c r="G30">
-        <v>-7.70367041546224</v>
+        <v>-10.95485125212322</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.887118072503774</v>
       </c>
       <c r="E31">
-        <v>-33.88918374137031</v>
+        <v>-40.28375811083248</v>
       </c>
       <c r="F31">
-        <v>3.247153154250815</v>
+        <v>1.10438954842575</v>
       </c>
       <c r="G31">
-        <v>-8.134369079575881</v>
+        <v>-12.68175098504648</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.154321653804052</v>
       </c>
       <c r="E32">
-        <v>-34.19435760474721</v>
+        <v>-37.24957637079116</v>
       </c>
       <c r="F32">
-        <v>2.84934206535158</v>
+        <v>0.8448454881798714</v>
       </c>
       <c r="G32">
-        <v>-7.613669924431613</v>
+        <v>-11.52658577730089</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.372188142679013</v>
       </c>
       <c r="E33">
-        <v>-33.48734280758867</v>
+        <v>-38.06152723189245</v>
       </c>
       <c r="F33">
-        <v>3.057846451354676</v>
+        <v>0.4808686924580849</v>
       </c>
       <c r="G33">
-        <v>-7.504637107095717</v>
+        <v>-13.20908116290591</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.537019215968047</v>
       </c>
       <c r="E34">
-        <v>-34.01014154635219</v>
+        <v>-36.54484618876948</v>
       </c>
       <c r="F34">
-        <v>3.759805093902226</v>
+        <v>0.9396429568662459</v>
       </c>
       <c r="G34">
-        <v>-7.967100455658666</v>
+        <v>-11.11711102063951</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.646845813823129</v>
       </c>
       <c r="E35">
-        <v>-32.37084754099754</v>
+        <v>-38.32458175852401</v>
       </c>
       <c r="F35">
-        <v>3.841989928678041</v>
+        <v>1.088734615451631</v>
       </c>
       <c r="G35">
-        <v>-8.30644130507058</v>
+        <v>-13.3272345332025</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.706644756323191</v>
       </c>
       <c r="E36">
-        <v>-32.69373453045545</v>
+        <v>-38.84575024664477</v>
       </c>
       <c r="F36">
-        <v>2.925030538462262</v>
+        <v>1.04822341813469</v>
       </c>
       <c r="G36">
-        <v>-8.115674428915618</v>
+        <v>-12.74279082369956</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.722061035932883</v>
       </c>
       <c r="E37">
-        <v>-32.29609602055292</v>
+        <v>-37.44655593317681</v>
       </c>
       <c r="F37">
-        <v>2.97908242135621</v>
+        <v>1.293056434132051</v>
       </c>
       <c r="G37">
-        <v>-7.908235645424885</v>
+        <v>-12.50657677838148</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.698622288121561</v>
       </c>
       <c r="E38">
-        <v>-31.2585954545516</v>
+        <v>-37.6044208013212</v>
       </c>
       <c r="F38">
-        <v>2.684254977020256</v>
+        <v>1.380461163605154</v>
       </c>
       <c r="G38">
-        <v>-8.756304717311064</v>
+        <v>-13.78357337251779</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.644067410496659</v>
       </c>
       <c r="E39">
-        <v>-31.28342281329865</v>
+        <v>-36.59077397215528</v>
       </c>
       <c r="F39">
-        <v>3.197670262922909</v>
+        <v>1.71736925782025</v>
       </c>
       <c r="G39">
-        <v>-9.090606916412208</v>
+        <v>-13.24166024155788</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.567986254942921</v>
       </c>
       <c r="E40">
-        <v>-30.47697631235369</v>
+        <v>-34.46736118877363</v>
       </c>
       <c r="F40">
-        <v>3.549183293090187</v>
+        <v>2.172705296685991</v>
       </c>
       <c r="G40">
-        <v>-8.735706502965717</v>
+        <v>-13.50693591089245</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.479648675674534</v>
       </c>
       <c r="E41">
-        <v>-30.30324593552342</v>
+        <v>-35.29128080667719</v>
       </c>
       <c r="F41">
-        <v>3.148299814715</v>
+        <v>1.509971882252046</v>
       </c>
       <c r="G41">
-        <v>-9.016987004709895</v>
+        <v>-14.44002641331819</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.384771503916068</v>
       </c>
       <c r="E42">
-        <v>-29.08369618593974</v>
+        <v>-32.56147365435042</v>
       </c>
       <c r="F42">
-        <v>3.347960786886282</v>
+        <v>1.512806715840683</v>
       </c>
       <c r="G42">
-        <v>-7.829150023037236</v>
+        <v>-13.98797804102179</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.289125970184531</v>
       </c>
       <c r="E43">
-        <v>-27.68702423249405</v>
+        <v>-33.5478205779611</v>
       </c>
       <c r="F43">
-        <v>3.758314826635797</v>
+        <v>2.432022886985962</v>
       </c>
       <c r="G43">
-        <v>-8.64820547381724</v>
+        <v>-12.95481471276219</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.197991090077629</v>
       </c>
       <c r="E44">
-        <v>-26.8471100443954</v>
+        <v>-32.49590814343037</v>
       </c>
       <c r="F44">
-        <v>3.562823752139867</v>
+        <v>1.710164979610916</v>
       </c>
       <c r="G44">
-        <v>-9.321865075057996</v>
+        <v>-15.48335973747443</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.115615553454584</v>
       </c>
       <c r="E45">
-        <v>-26.39226105811698</v>
+        <v>-32.27567260277834</v>
       </c>
       <c r="F45">
-        <v>3.144752313464416</v>
+        <v>1.746412840603494</v>
       </c>
       <c r="G45">
-        <v>-8.570377858734515</v>
+        <v>-14.98361468032098</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.041314447555825</v>
       </c>
       <c r="E46">
-        <v>-26.97532925744858</v>
+        <v>-32.33342423179815</v>
       </c>
       <c r="F46">
-        <v>3.391365414910731</v>
+        <v>1.682505555797766</v>
       </c>
       <c r="G46">
-        <v>-9.203777915672193</v>
+        <v>-14.32574803657532</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.972745008593504</v>
       </c>
       <c r="E47">
-        <v>-26.81289289479344</v>
+        <v>-33.15630230067995</v>
       </c>
       <c r="F47">
-        <v>3.349061462497513</v>
+        <v>1.622848937669077</v>
       </c>
       <c r="G47">
-        <v>-9.035867045920359</v>
+        <v>-15.14318132004108</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.907731277583298</v>
       </c>
       <c r="E48">
-        <v>-26.88797499384062</v>
+        <v>-31.40803056833072</v>
       </c>
       <c r="F48">
-        <v>3.392488262404778</v>
+        <v>1.914941321889067</v>
       </c>
       <c r="G48">
-        <v>-8.951471308487717</v>
+        <v>-16.45051906404481</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.84472001160604</v>
       </c>
       <c r="E49">
-        <v>-25.02787259587197</v>
+        <v>-31.58098657610567</v>
       </c>
       <c r="F49">
-        <v>4.065883185061462</v>
+        <v>1.990351062758632</v>
       </c>
       <c r="G49">
-        <v>-8.782011103423503</v>
+        <v>-14.17871181172136</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.780203084097523</v>
       </c>
       <c r="E50">
-        <v>-24.97266144077045</v>
+        <v>-31.5450486063808</v>
       </c>
       <c r="F50">
-        <v>3.376760478958548</v>
+        <v>1.394362934130882</v>
       </c>
       <c r="G50">
-        <v>-9.832520035036115</v>
+        <v>-14.12210313827259</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.710110155577432</v>
       </c>
       <c r="E51">
-        <v>-24.22794030478703</v>
+        <v>-30.45337617006272</v>
       </c>
       <c r="F51">
-        <v>3.460522684826141</v>
+        <v>2.171520684661243</v>
       </c>
       <c r="G51">
-        <v>-9.80751879512354</v>
+        <v>-14.19558235178948</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.634214898287149</v>
       </c>
       <c r="E52">
-        <v>-23.82737866491256</v>
+        <v>-28.22304158688596</v>
       </c>
       <c r="F52">
-        <v>3.668439515934609</v>
+        <v>2.03977060584992</v>
       </c>
       <c r="G52">
-        <v>-9.023750449246625</v>
+        <v>-14.90627371543252</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.555851036467449</v>
       </c>
       <c r="E53">
-        <v>-24.27926150071596</v>
+        <v>-31.68418144179246</v>
       </c>
       <c r="F53">
-        <v>3.861263629668938</v>
+        <v>2.52984365026491</v>
       </c>
       <c r="G53">
-        <v>-9.041733332615946</v>
+        <v>-15.55250048106211</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.477718640158417</v>
       </c>
       <c r="E54">
-        <v>-23.72037082411131</v>
+        <v>-28.95439466759873</v>
       </c>
       <c r="F54">
-        <v>3.418402442299113</v>
+        <v>1.637360434972249</v>
       </c>
       <c r="G54">
-        <v>-11.02689534414884</v>
+        <v>-13.71210862596155</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.400668821931479</v>
       </c>
       <c r="E55">
-        <v>-22.24818656658772</v>
+        <v>-28.58153823170318</v>
       </c>
       <c r="F55">
-        <v>4.035186213302499</v>
+        <v>2.474634078346776</v>
       </c>
       <c r="G55">
-        <v>-9.691086908507373</v>
+        <v>-15.11333509673178</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.329003635707506</v>
       </c>
       <c r="E56">
-        <v>-21.4428925622777</v>
+        <v>-28.23584358290564</v>
       </c>
       <c r="F56">
-        <v>3.536420207117661</v>
+        <v>2.587053442754245</v>
       </c>
       <c r="G56">
-        <v>-10.44912900499861</v>
+        <v>-14.89747428538914</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.266814417528585</v>
       </c>
       <c r="E57">
-        <v>-21.68073707410857</v>
+        <v>-27.39062202327001</v>
       </c>
       <c r="F57">
-        <v>4.020172681224133</v>
+        <v>2.195086228682982</v>
       </c>
       <c r="G57">
-        <v>-10.28313494111401</v>
+        <v>-16.17863554581385</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.216000710097152</v>
       </c>
       <c r="E58">
-        <v>-20.99616312989503</v>
+        <v>-28.81619922630665</v>
       </c>
       <c r="F58">
-        <v>3.452512300305848</v>
+        <v>1.898364672072162</v>
       </c>
       <c r="G58">
-        <v>-10.04363683462098</v>
+        <v>-15.47722198604462</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.175163791894893</v>
       </c>
       <c r="E59">
-        <v>-20.37725205879271</v>
+        <v>-25.4497225920565</v>
       </c>
       <c r="F59">
-        <v>3.586436807339069</v>
+        <v>1.798892103523411</v>
       </c>
       <c r="G59">
-        <v>-10.55611921573678</v>
+        <v>-15.44909890168851</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.14402919604946</v>
       </c>
       <c r="E60">
-        <v>-20.13699839878977</v>
+        <v>-27.81513929064505</v>
       </c>
       <c r="F60">
-        <v>3.778141240991184</v>
+        <v>2.232016666925114</v>
       </c>
       <c r="G60">
-        <v>-9.363849413587033</v>
+        <v>-15.51297587786875</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.121382632833697</v>
       </c>
       <c r="E61">
-        <v>-20.83658423433873</v>
+        <v>-25.4738140737773</v>
       </c>
       <c r="F61">
-        <v>4.036364490503585</v>
+        <v>2.056019428542328</v>
       </c>
       <c r="G61">
-        <v>-10.74306241179388</v>
+        <v>-14.50971836273816</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.104907401427333</v>
       </c>
       <c r="E62">
-        <v>-19.4669246283488</v>
+        <v>-25.37794175056091</v>
       </c>
       <c r="F62">
-        <v>4.033873321098599</v>
+        <v>1.254786180685457</v>
       </c>
       <c r="G62">
-        <v>-10.56680896728308</v>
+        <v>-16.29019099885068</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.089325811001513</v>
       </c>
       <c r="E63">
-        <v>-19.99338690258452</v>
+        <v>-24.37713993791775</v>
       </c>
       <c r="F63">
-        <v>3.388907503329969</v>
+        <v>2.336674288641015</v>
       </c>
       <c r="G63">
-        <v>-11.53850043069673</v>
+        <v>-16.95558913369818</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.070734670530581</v>
       </c>
       <c r="E64">
-        <v>-18.83516627648672</v>
+        <v>-25.08521666223109</v>
       </c>
       <c r="F64">
-        <v>3.397006575381526</v>
+        <v>1.433263502531821</v>
       </c>
       <c r="G64">
-        <v>-11.20902500699184</v>
+        <v>-16.46427769130602</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.046172520245108</v>
       </c>
       <c r="E65">
-        <v>-17.46656633341458</v>
+        <v>-24.50192656767311</v>
       </c>
       <c r="F65">
-        <v>3.569388213159364</v>
+        <v>1.339807432755824</v>
       </c>
       <c r="G65">
-        <v>-11.11942509197146</v>
+        <v>-14.3667921801712</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.013975942375303</v>
       </c>
       <c r="E66">
-        <v>-18.33672167093645</v>
+        <v>-26.29572757769547</v>
       </c>
       <c r="F66">
-        <v>2.930695454521789</v>
+        <v>0.9330975003177346</v>
       </c>
       <c r="G66">
-        <v>-10.780332533475</v>
+        <v>-15.1957097461127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.971557571421304</v>
       </c>
       <c r="E67">
-        <v>-19.1058467533472</v>
+        <v>-25.12461891457183</v>
       </c>
       <c r="F67">
-        <v>3.469969490611737</v>
+        <v>1.180624400077259</v>
       </c>
       <c r="G67">
-        <v>-11.83656870887055</v>
+        <v>-17.25533585846041</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.917316836842113</v>
       </c>
       <c r="E68">
-        <v>-17.79627999743905</v>
+        <v>-23.45411466635633</v>
       </c>
       <c r="F68">
-        <v>3.202975677739631</v>
+        <v>0.8489979650901537</v>
       </c>
       <c r="G68">
-        <v>-11.72016330661869</v>
+        <v>-14.40314031491963</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.851394534985129</v>
       </c>
       <c r="E69">
-        <v>-18.28771452522544</v>
+        <v>-23.37537356031095</v>
       </c>
       <c r="F69">
-        <v>2.91464459506881</v>
+        <v>1.314696191760616</v>
       </c>
       <c r="G69">
-        <v>-10.48528347283299</v>
+        <v>-15.8088128483491</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.775049891251496</v>
       </c>
       <c r="E70">
-        <v>-18.0188861942341</v>
+        <v>-23.96878932275008</v>
       </c>
       <c r="F70">
-        <v>2.975742385580549</v>
+        <v>1.609442867094882</v>
       </c>
       <c r="G70">
-        <v>-11.46027555014929</v>
+        <v>-14.89108989831666</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.688402954877605</v>
       </c>
       <c r="E71">
-        <v>-18.28796359129586</v>
+        <v>-27.83697559231004</v>
       </c>
       <c r="F71">
-        <v>2.786657401512571</v>
+        <v>1.475697318830105</v>
       </c>
       <c r="G71">
-        <v>-10.62014516646628</v>
+        <v>-15.5973054043906</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.590769405983907</v>
       </c>
       <c r="E72">
-        <v>-18.4255431601229</v>
+        <v>-22.76733988377506</v>
       </c>
       <c r="F72">
-        <v>2.975633109872383</v>
+        <v>1.465685130032697</v>
       </c>
       <c r="G72">
-        <v>-10.7586087336463</v>
+        <v>-15.63352773840854</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.484671456747753</v>
       </c>
       <c r="E73">
-        <v>-18.54810178066649</v>
+        <v>-23.15531689438222</v>
       </c>
       <c r="F73">
-        <v>2.499854595050149</v>
+        <v>0.6887316775654279</v>
       </c>
       <c r="G73">
-        <v>-11.16907665396946</v>
+        <v>-15.67594410313045</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.374369221857592</v>
       </c>
       <c r="E74">
-        <v>-18.49219324056779</v>
+        <v>-26.1180981847446</v>
       </c>
       <c r="F74">
-        <v>2.524535068036358</v>
+        <v>0.1865131924849321</v>
       </c>
       <c r="G74">
-        <v>-11.78636759631304</v>
+        <v>-13.80509853961414</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.263579837388983</v>
       </c>
       <c r="E75">
-        <v>-19.13193076363138</v>
+        <v>-28.06533747956884</v>
       </c>
       <c r="F75">
-        <v>2.453725992851144</v>
+        <v>-0.08716069193849708</v>
       </c>
       <c r="G75">
-        <v>-11.5658024997591</v>
+        <v>-15.56501434320055</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.154954647886541</v>
       </c>
       <c r="E76">
-        <v>-17.57066236542889</v>
+        <v>-21.6964644643372</v>
       </c>
       <c r="F76">
-        <v>2.798929538651311</v>
+        <v>0.6194318741176286</v>
       </c>
       <c r="G76">
-        <v>-10.178644192258</v>
+        <v>-16.52894092205183</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.054073479524331</v>
       </c>
       <c r="E77">
-        <v>-17.81721513277651</v>
+        <v>-24.47228317681891</v>
       </c>
       <c r="F77">
-        <v>1.720837573775062</v>
+        <v>-0.1089754490707178</v>
       </c>
       <c r="G77">
-        <v>-9.755265144331684</v>
+        <v>-15.23227141104841</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.96705331856173</v>
       </c>
       <c r="E78">
-        <v>-18.47742135835477</v>
+        <v>-24.67622753222835</v>
       </c>
       <c r="F78">
-        <v>2.152213725846121</v>
+        <v>-0.03190994366656108</v>
       </c>
       <c r="G78">
-        <v>-9.515088376003098</v>
+        <v>-14.27681817350489</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.8994981389253</v>
       </c>
       <c r="E79">
-        <v>-19.05059937045362</v>
+        <v>-25.99031823367016</v>
       </c>
       <c r="F79">
-        <v>1.965681675713832</v>
+        <v>0.08206857921465824</v>
       </c>
       <c r="G79">
-        <v>-9.684244010877698</v>
+        <v>-12.4096837315381</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.855307391638819</v>
       </c>
       <c r="E80">
-        <v>-20.52302816557363</v>
+        <v>-26.83300384786151</v>
       </c>
       <c r="F80">
-        <v>2.470063503074817</v>
+        <v>0.3216017233660015</v>
       </c>
       <c r="G80">
-        <v>-9.97799202712277</v>
+        <v>-12.87201465827947</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.839605050460824</v>
       </c>
       <c r="E81">
-        <v>-20.82769031138767</v>
+        <v>-26.01142997949392</v>
       </c>
       <c r="F81">
-        <v>1.943699837607532</v>
+        <v>0.06314883649586088</v>
       </c>
       <c r="G81">
-        <v>-9.121507548475764</v>
+        <v>-13.96173369125921</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.858229970653804</v>
       </c>
       <c r="E82">
-        <v>-20.93156444817561</v>
+        <v>-23.9612992267414</v>
       </c>
       <c r="F82">
-        <v>1.913935668632763</v>
+        <v>-0.2922316035169202</v>
       </c>
       <c r="G82">
-        <v>-8.242580881618039</v>
+        <v>-12.21651008877608</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.918202953199978</v>
       </c>
       <c r="E83">
-        <v>-21.28321856876725</v>
+        <v>-26.92359597038495</v>
       </c>
       <c r="F83">
-        <v>1.686995362068036</v>
+        <v>0.5128128326254563</v>
       </c>
       <c r="G83">
-        <v>-9.45457491409076</v>
+        <v>-13.8934669316939</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.024566046752112</v>
       </c>
       <c r="E84">
-        <v>-23.09636521975036</v>
+        <v>-25.91657656292926</v>
       </c>
       <c r="F84">
-        <v>1.686198757992571</v>
+        <v>-0.1371147357762459</v>
       </c>
       <c r="G84">
-        <v>-8.606075471284477</v>
+        <v>-11.75375210166014</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.181730399652063</v>
       </c>
       <c r="E85">
-        <v>-24.08069244395363</v>
+        <v>-28.39683083387833</v>
       </c>
       <c r="F85">
-        <v>1.638309074815597</v>
+        <v>0.1132081967769864</v>
       </c>
       <c r="G85">
-        <v>-9.118385704032232</v>
+        <v>-14.69418030491358</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.393030972693975</v>
       </c>
       <c r="E86">
-        <v>-24.25431413740771</v>
+        <v>-29.67249516912806</v>
       </c>
       <c r="F86">
-        <v>1.687969341206032</v>
+        <v>0.2400234479558001</v>
       </c>
       <c r="G86">
-        <v>-8.483820335064731</v>
+        <v>-12.79505440612804</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.664676502509202</v>
       </c>
       <c r="E87">
-        <v>-25.28710056196705</v>
+        <v>-30.37723214386074</v>
       </c>
       <c r="F87">
-        <v>1.181709238629334</v>
+        <v>-0.8240281721271209</v>
       </c>
       <c r="G87">
-        <v>-7.3505444544248</v>
+        <v>-11.69418214522649</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.99855668935961</v>
       </c>
       <c r="E88">
-        <v>-26.31053568770055</v>
+        <v>-29.11758728541315</v>
       </c>
       <c r="F88">
-        <v>1.076592342197957</v>
+        <v>-1.007654121904578</v>
       </c>
       <c r="G88">
-        <v>-7.959323984186918</v>
+        <v>-9.76323031689917</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.393306879868582</v>
       </c>
       <c r="E89">
-        <v>-28.06524691008869</v>
+        <v>-32.90918800255539</v>
       </c>
       <c r="F89">
-        <v>1.123696507240872</v>
+        <v>-0.9474075733223888</v>
       </c>
       <c r="G89">
-        <v>-7.616142901949448</v>
+        <v>-9.613775738528773</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.842553909821802</v>
       </c>
       <c r="E90">
-        <v>-29.60654020944334</v>
+        <v>-32.74611991777618</v>
       </c>
       <c r="F90">
-        <v>0.9657408466467725</v>
+        <v>-1.205174715531144</v>
       </c>
       <c r="G90">
-        <v>-7.190413366690253</v>
+        <v>-9.987791241919012</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.345846241116265</v>
       </c>
       <c r="E91">
-        <v>-30.71811755326214</v>
+        <v>-32.7624880870769</v>
       </c>
       <c r="F91">
-        <v>1.302720207628063</v>
+        <v>-1.446285230774265</v>
       </c>
       <c r="G91">
-        <v>-6.037827073919753</v>
+        <v>-11.70969867216906</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.896716989387247</v>
       </c>
       <c r="E92">
-        <v>-31.56306740445732</v>
+        <v>-35.33173592922471</v>
       </c>
       <c r="F92">
-        <v>0.7373625351108269</v>
+        <v>-0.9428940114633864</v>
       </c>
       <c r="G92">
-        <v>-7.4611034332543</v>
+        <v>-12.29543349443231</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.484398856838231</v>
       </c>
       <c r="E93">
-        <v>-32.84049558033303</v>
+        <v>-38.07523492271367</v>
       </c>
       <c r="F93">
-        <v>0.8688180446218783</v>
+        <v>-1.340347182825732</v>
       </c>
       <c r="G93">
-        <v>-7.121004468913893</v>
+        <v>-11.12278529569383</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.090273067358119</v>
       </c>
       <c r="E94">
-        <v>-34.92575144172606</v>
+        <v>-37.89002260003696</v>
       </c>
       <c r="F94">
-        <v>0.5456430562525161</v>
+        <v>-2.231371804970274</v>
       </c>
       <c r="G94">
-        <v>-6.071051708951879</v>
+        <v>-10.23687668829378</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.704288817170092</v>
       </c>
       <c r="E95">
-        <v>-36.46827422177379</v>
+        <v>-38.18048118712593</v>
       </c>
       <c r="F95">
-        <v>0.06891590158693363</v>
+        <v>-1.322494857893941</v>
       </c>
       <c r="G95">
-        <v>-6.169457675106715</v>
+        <v>-12.7739596099518</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.312643375477887</v>
       </c>
       <c r="E96">
-        <v>-37.63597747244365</v>
+        <v>-41.03407191221537</v>
       </c>
       <c r="F96">
-        <v>0.09156210432476</v>
+        <v>-2.56635569649811</v>
       </c>
       <c r="G96">
-        <v>-6.618182259681689</v>
+        <v>-11.26101712468609</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.895722221580376</v>
       </c>
       <c r="E97">
-        <v>-40.17822655255773</v>
+        <v>-41.84334870941512</v>
       </c>
       <c r="F97">
-        <v>-0.1134106174869059</v>
+        <v>-2.475219755888232</v>
       </c>
       <c r="G97">
-        <v>-7.001242173485219</v>
+        <v>-9.950848864246286</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.43947495023254</v>
       </c>
       <c r="E98">
-        <v>-42.03374160635661</v>
+        <v>-45.10383640951576</v>
       </c>
       <c r="F98">
-        <v>-0.371387600729457</v>
+        <v>-2.245025725520235</v>
       </c>
       <c r="G98">
-        <v>-7.445848439409339</v>
+        <v>-9.829576960051703</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.92710836618152</v>
       </c>
       <c r="E99">
-        <v>-44.58894212213263</v>
+        <v>-45.73435395949974</v>
       </c>
       <c r="F99">
-        <v>-0.2009404597273287</v>
+        <v>-2.025552592346806</v>
       </c>
       <c r="G99">
-        <v>-6.69843981519024</v>
+        <v>-10.57981610070688</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.36304137273456</v>
       </c>
       <c r="E100">
-        <v>-46.39752407131601</v>
+        <v>-46.23094415494386</v>
       </c>
       <c r="F100">
-        <v>-0.9362970844726233</v>
+        <v>-2.933090516071634</v>
       </c>
       <c r="G100">
-        <v>-6.829371891268416</v>
+        <v>-12.63327135616939</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.72310861300802</v>
       </c>
       <c r="E101">
-        <v>-47.21977268231074</v>
+        <v>-49.07174080884312</v>
       </c>
       <c r="F101">
-        <v>-0.7585815251715857</v>
+        <v>-2.850242900370208</v>
       </c>
       <c r="G101">
-        <v>-6.609558288551887</v>
+        <v>-11.62160836591459</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.03329489559182</v>
       </c>
       <c r="E102">
-        <v>-49.42362361737214</v>
+        <v>-51.46530310550785</v>
       </c>
       <c r="F102">
-        <v>-1.162774157057084</v>
+        <v>-3.619227144670986</v>
       </c>
       <c r="G102">
-        <v>-7.354192675609077</v>
+        <v>-12.59560065847803</v>
       </c>
     </row>
   </sheetData>
